--- a/public/data/morning_meeting_data.xlsx
+++ b/public/data/morning_meeting_data.xlsx
@@ -2,31 +2,31 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R5ef4587201544eb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="markets" sheetId="2" r:id="Ra2e14b651ecf4fc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="placeholders" sheetId="3" r:id="R3da03fd26f3e4dc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mainChart" sheetId="4" r:id="R62c920b134644423"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="marketStats" sheetId="5" r:id="R094ce615b7044512"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="snapshot" sheetId="6" r:id="R5aed435655f7489b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="news" sheetId="7" r:id="Rc43f4b56972f478d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="drivers" sheetId="8" r:id="Ra7970ca8d83d414f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="conclusions" sheetId="9" r:id="R9be64e2b2d064a1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="deeper" sheetId="10" r:id="R7545b33c59be4971"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mapHotspots" sheetId="11" r:id="Racd8e24c1f5d47e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="industryBreakdown" sheetId="12" r:id="Rd38019057aec4165"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="breadthRows" sheetId="13" r:id="R6d0d4069391e4978"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fxRates" sheetId="14" r:id="Rbae5f20618bb4ea4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fxStrength" sheetId="15" r:id="Rd70604e654cb4852"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fxHeatmap" sheetId="16" r:id="R5077450eba604424"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="commodityTiles" sheetId="17" r:id="R1760a5ea30cc4db6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bondCurve" sheetId="18" r:id="R86f5dbc8d5124385"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bondTenorMoves" sheetId="19" r:id="Rf8994b41632447eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bondMetricCards" sheetId="20" r:id="R0c3248c5d3a34bb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cryptoStructure" sheetId="21" r:id="R12c23ef6ddf6435c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cryptoDerivatives" sheetId="22" r:id="R03cf64b43c8d43f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="23" r:id="Reeb6699a53174dbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="validation" sheetId="24" r:id="Rf3c7cf033d904c1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="update_notes" sheetId="25" r:id="Rfcb7fa5fcbf946c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R986de4d7fa06452e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="markets" sheetId="2" r:id="R488deae5c8664a95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="placeholders" sheetId="3" r:id="Rdb68df62fe864256"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mainChart" sheetId="4" r:id="R32046e9e969140ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="marketStats" sheetId="5" r:id="R1e3be5bad0c34130"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="snapshot" sheetId="6" r:id="R6f7108ce37c74bf6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="news" sheetId="7" r:id="Rc4aa6c7a9df84fb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="drivers" sheetId="8" r:id="R1f0f4cf1fb644513"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="conclusions" sheetId="9" r:id="R73faec710ad0437b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="deeper" sheetId="10" r:id="R35ff195daf944c6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mapHotspots" sheetId="11" r:id="Rb946eb9162ad4d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="industryBreakdown" sheetId="12" r:id="Rb2db31a041b24297"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="breadthRows" sheetId="13" r:id="R564cee24d3494cdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fxRates" sheetId="14" r:id="Rbbcbd1f5a1cf4630"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fxStrength" sheetId="15" r:id="Rc1dbec0bec594328"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fxHeatmap" sheetId="16" r:id="Raaba1e0b10e24c81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="commodityTiles" sheetId="17" r:id="R50fa8e49d3cc4017"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bondCurve" sheetId="18" r:id="R759707ad6e714014"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bondTenorMoves" sheetId="19" r:id="Rb881772fa1824dc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bondMetricCards" sheetId="20" r:id="Rcd7704fdc0814b92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cryptoStructure" sheetId="21" r:id="R0ee0888f41fd4fe7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cryptoDerivatives" sheetId="22" r:id="Rddd7869ef6f24a26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sources" sheetId="23" r:id="R760fce14ceb94987"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="validation" sheetId="24" r:id="R6f6bff345b984af5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="update_notes" sheetId="25" r:id="Rc0706bba8ae547c5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3800,7 +3800,7 @@
         <x:v>Majors,Altcoins,DeFi,Global</x:v>
       </x:c>
       <x:c r="F6" t="str">
-        <x:v>Investing.com / CoinDesk / Economic Times</x:v>
+        <x:v>Yahoo Finance / CoinDesk / Benzinga</x:v>
       </x:c>
       <x:c r="G6" t="str">
         <x:v>FOCUS TOKEN</x:v>
@@ -3815,22 +3815,22 @@
         <x:v>BTC spot market</x:v>
       </x:c>
       <x:c r="K6" t="str">
-        <x:v>77,518.0</x:v>
+        <x:v>$77,519.00</x:v>
       </x:c>
       <x:c r="L6" t="str">
-        <x:v>-0.95%</x:v>
+        <x:v>-0.11%</x:v>
       </x:c>
       <x:c r="M6" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N6" t="str">
-        <x:v>Bitcoin - Last Close</x:v>
+        <x:v>Bitcoin - Live Snapshot</x:v>
       </x:c>
       <x:c r="O6" t="str">
-        <x:v>77,518.0</x:v>
+        <x:v>$77,519.00</x:v>
       </x:c>
       <x:c r="P6" t="str">
-        <x:v>-739.7 (-0.95%)</x:v>
+        <x:v>-85.00 (-0.11%)</x:v>
       </x:c>
       <x:c r="Q6" t="str">
         <x:v>red</x:v>
@@ -3839,16 +3839,16 @@
         <x:v>crypto</x:v>
       </x:c>
       <x:c r="S6" t="str">
-        <x:v>ON-CHAIN SNAPSHOT</x:v>
+        <x:v>CRYPTO SNAPSHOT</x:v>
       </x:c>
       <x:c r="T6" t="str">
-        <x:v>https://www.investing.com/crypto/bitcoin/historical-data</x:v>
+        <x:v>https://finance.yahoo.com/quote/BTC-USD</x:v>
       </x:c>
       <x:c r="U6" t="str">
-        <x:v>2026-04-24</x:v>
+        <x:v>2026-04-26</x:v>
       </x:c>
       <x:c r="V6" t="str">
-        <x:v>BTC/USD daily historical data from Investing.com.</x:v>
+        <x:v>Crypto trades 24/7; updated to latest available live snapshot. Non-crypto markets remain latest close.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4013,7 +4013,7 @@
         <x:v>Bitcoin</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>Focus: $77,518.0</x:v>
+        <x:v>Focus: $77,519.00</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>#f59e0b</x:v>
@@ -4022,7 +4022,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2" t="str">
-        <x:v>https://www.investing.com/crypto/bitcoin/historical-data</x:v>
+        <x:v>https://finance.yahoo.com/quote/BTC-USD</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -4030,19 +4030,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>ETF inflow streak</x:v>
+        <x:v>Ethereum</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>$2.1B / 8 days</x:v>
+        <x:v>$2,315.48 / -0.23%</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>#22c55e</x:v>
+        <x:v>#818cf8</x:v>
       </x:c>
       <x:c r="E3" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>https://www.coindesk.com/markets/2026/04/24/bitcoin-etfs-just-pulled-usd2-billion-in-8-days-while-short-term-holders-quietly-started-selling</x:v>
+        <x:v>https://finance.yahoo.com/quote/ETH-USD</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -4050,19 +4050,19 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>Exchange reserves</x:v>
+        <x:v>Solana</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>near record lows</x:v>
+        <x:v>$86.08 / -0.35%</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>#818cf8</x:v>
+        <x:v>#22c55e</x:v>
       </x:c>
       <x:c r="E4" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>https://m.economictimes.com/markets/cryptocurrency/bitcoin-holds-near-78000-on-strong-etf-inflows-exchange-reserves-near-record-lows/articleshow/130484642.cms</x:v>
+        <x:v>https://finance.yahoo.com/quote/SOL-USD</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -4070,18 +4070,20 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>Other crypto</x:v>
+        <x:v>ETF / stablecoin backdrop</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>N/A</x:v>
+        <x:v>BTC MTD +13.71%; USDT growth noted</x:v>
       </x:c>
       <x:c r="D5" t="str">
         <x:v>#e5e7eb</x:v>
       </x:c>
       <x:c r="E5" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F5" t="str"/>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>https://www.coindesk.com/markets/2026/04/24/bitcoin-is-on-track-for-its-best-month-in-a-year-usd5-billion-usdt-growth-fuels-the-rebound</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4125,19 +4127,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>BTC spot close</x:v>
+        <x:v>BTC spot</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>$77,518.0</x:v>
+        <x:v>$77,519.00</x:v>
       </x:c>
       <x:c r="D2" t="str">
-        <x:v>-0.95%</x:v>
+        <x:v>-0.11%</x:v>
       </x:c>
       <x:c r="E2" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F2" t="str">
-        <x:v>https://www.investing.com/crypto/bitcoin/historical-data</x:v>
+        <x:v>https://finance.yahoo.com/quote/BTC-USD</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -4145,19 +4147,19 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>ETF inflows</x:v>
+        <x:v>BTC 24H range</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>$2.1B</x:v>
+        <x:v>$77,218.00 - $77,878.00</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>8-day streak</x:v>
+        <x:v>Live snapshot</x:v>
       </x:c>
       <x:c r="E3" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>https://www.coindesk.com/markets/2026/04/24/bitcoin-etfs-just-pulled-usd2-billion-in-8-days-while-short-term-holders-quietly-started-selling</x:v>
+        <x:v>https://finance.yahoo.com/quote/BTC-USD</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -4165,36 +4167,40 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>Open Interest</x:v>
+        <x:v>ETH spot</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>N/A</x:v>
+        <x:v>$2,315.48</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>Not sourced</x:v>
+        <x:v>-0.23%</x:v>
       </x:c>
       <x:c r="E4" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F4" t="str"/>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F4" t="str">
+        <x:v>https://finance.yahoo.com/quote/ETH-USD</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>Funding</x:v>
+        <x:v>SOL spot</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>N/A</x:v>
+        <x:v>$86.08</x:v>
       </x:c>
       <x:c r="D5" t="str">
-        <x:v>Not sourced</x:v>
+        <x:v>-0.35%</x:v>
       </x:c>
       <x:c r="E5" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F5" t="str"/>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>https://finance.yahoo.com/quote/SOL-USD</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4633,6 +4639,54 @@
         <x:v>https://tradingeconomics.com/brazil/stock-market</x:v>
       </x:c>
     </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="str">
+        <x:v>btc_yahoo_live</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>https://finance.yahoo.com/quote/BTC-USD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str">
+        <x:v>eth_yahoo_live</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>https://finance.yahoo.com/quote/ETH-USD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str">
+        <x:v>sol_yahoo_live</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>https://finance.yahoo.com/quote/SOL-USD</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="str">
+        <x:v>coindesk_btc_april_rebound</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>https://www.coindesk.com/markets/2026/04/24/bitcoin-is-on-track-for-its-best-month-in-a-year-usd5-billion-usdt-growth-fuels-the-rebound</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str">
+        <x:v>yahoo_btc_best_april</x:v>
+      </x:c>
+      <x:c r="B58" t="str">
+        <x:v>https://finance.yahoo.com/markets/crypto/articles/bitcoin-1-week-secure-best-165709121.html</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="str">
+        <x:v>benzinga_btc_etf_inflows</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>https://www.benzinga.com/crypto/cryptocurrency/26/04/52029356/bitcoin-etfs-add-2-1b-in-8-days-last-time-this-happened-bitcoin-hit-an-all-time-high</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4937,10 +4991,10 @@
         <x:v>2026-04-26</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>https://api.binance.com/api/v3/ticker/24hr?symbol=BTCUSDT</x:v>
+        <x:v>https://finance.yahoo.com/quote/BTC-USD</x:v>
       </x:c>
       <x:c r="D7" t="str">
-        <x:v>Crypto trades 24/7; API can update when deployed.</x:v>
+        <x:v>Crypto trades 24/7; crypto block was refreshed with current BTC/ETH/SOL live snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -6229,6 +6283,26 @@
         <x:v>BTC/USD daily close.</x:v>
       </x:c>
     </x:row>
+    <x:row r="43">
+      <x:c r="A43" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B43" t="str">
+        <x:v>Crypto</x:v>
+      </x:c>
+      <x:c r="C43" t="str">
+        <x:v>Apr 26 live</x:v>
+      </x:c>
+      <x:c r="D43" t="n">
+        <x:v>77519</x:v>
+      </x:c>
+      <x:c r="E43" t="str">
+        <x:v>https://finance.yahoo.com/quote/BTC-USD</x:v>
+      </x:c>
+      <x:c r="F43" t="str">
+        <x:v>BTC/USD live/current snapshot appended; Apr 25 not filled to avoid unsourced value.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6754,16 +6828,16 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>LAST</x:v>
       </x:c>
       <x:c r="D26" t="str">
-        <x:v>$78,257.7</x:v>
+        <x:v>$77,519.00</x:v>
       </x:c>
       <x:c r="E26" t="str">
-        <x:v>https://www.investing.com/crypto/bitcoin/historical-data</x:v>
+        <x:v>https://finance.yahoo.com/quote/BTC-USD</x:v>
       </x:c>
       <x:c r="F26" t="str">
-        <x:v>Investing.com BTC.</x:v>
+        <x:v>BTC-USD live snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -6774,16 +6848,16 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>HIGH</x:v>
+        <x:v>24H HIGH</x:v>
       </x:c>
       <x:c r="D27" t="str">
-        <x:v>$78,526.3</x:v>
+        <x:v>$77,878.00</x:v>
       </x:c>
       <x:c r="E27" t="str">
-        <x:v>https://www.investing.com/crypto/bitcoin/historical-data</x:v>
+        <x:v>https://finance.yahoo.com/quote/BTC-USD</x:v>
       </x:c>
       <x:c r="F27" t="str">
-        <x:v>Investing.com BTC.</x:v>
+        <x:v>BTC intraday/high from live market snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -6794,16 +6868,16 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>LOW</x:v>
+        <x:v>24H LOW</x:v>
       </x:c>
       <x:c r="D28" t="str">
-        <x:v>$77,380.4</x:v>
+        <x:v>$77,218.00</x:v>
       </x:c>
       <x:c r="E28" t="str">
-        <x:v>https://www.investing.com/crypto/bitcoin/historical-data</x:v>
+        <x:v>https://finance.yahoo.com/quote/BTC-USD</x:v>
       </x:c>
       <x:c r="F28" t="str">
-        <x:v>Investing.com BTC.</x:v>
+        <x:v>BTC intraday/low from live market snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -6814,16 +6888,16 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>VOLUME</x:v>
+        <x:v>24H MOVE</x:v>
       </x:c>
       <x:c r="D29" t="str">
-        <x:v>47.65K</x:v>
+        <x:v>-0.11%</x:v>
       </x:c>
       <x:c r="E29" t="str">
-        <x:v>https://www.investing.com/crypto/bitcoin/historical-data</x:v>
+        <x:v>https://finance.yahoo.com/quote/BTC-USD</x:v>
       </x:c>
       <x:c r="F29" t="str">
-        <x:v>Investing.com BTC.</x:v>
+        <x:v>Calculated from current price and previous close/change.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -6834,16 +6908,16 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>ETF FLOWS</x:v>
+        <x:v>ETH</x:v>
       </x:c>
       <x:c r="D30" t="str">
-        <x:v>$2.1B / 8 days</x:v>
+        <x:v>$2,315.48 / -0.23%</x:v>
       </x:c>
       <x:c r="E30" t="str">
-        <x:v>https://www.coindesk.com/markets/2026/04/24/bitcoin-etfs-just-pulled-usd2-billion-in-8-days-while-short-term-holders-quietly-started-selling</x:v>
+        <x:v>https://finance.yahoo.com/quote/ETH-USD</x:v>
       </x:c>
       <x:c r="F30" t="str">
-        <x:v>CoinDesk ETF inflow streak.</x:v>
+        <x:v>ETH live snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -6854,16 +6928,16 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>1M</x:v>
+        <x:v>SOL</x:v>
       </x:c>
       <x:c r="D31" t="str">
-        <x:v>+10.48%</x:v>
+        <x:v>$86.08 / -0.35%</x:v>
       </x:c>
       <x:c r="E31" t="str">
-        <x:v>https://fortune.com/article/price-of-bitcoin-04-24-2026/</x:v>
+        <x:v>https://finance.yahoo.com/quote/SOL-USD</x:v>
       </x:c>
       <x:c r="F31" t="str">
-        <x:v>Fortune monthly comparison.</x:v>
+        <x:v>SOL live snapshot.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -7470,16 +7544,16 @@
         <x:v>BTC/USD</x:v>
       </x:c>
       <x:c r="D26" t="str">
-        <x:v>77,518.0</x:v>
+        <x:v>$77,519.00</x:v>
       </x:c>
       <x:c r="E26" t="str">
-        <x:v>-0.95%</x:v>
+        <x:v>-0.11%</x:v>
       </x:c>
       <x:c r="F26" t="str">
-        <x:v>https://www.investing.com/crypto/bitcoin/historical-data</x:v>
+        <x:v>https://finance.yahoo.com/quote/BTC-USD</x:v>
       </x:c>
       <x:c r="G26" t="str">
-        <x:v>Investing.com.</x:v>
+        <x:v>Updated live snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -7490,19 +7564,19 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>ETF inflow streak</x:v>
+        <x:v>BTC 24H high</x:v>
       </x:c>
       <x:c r="D27" t="str">
-        <x:v>$2.1B</x:v>
+        <x:v>$77,878.00</x:v>
       </x:c>
       <x:c r="E27" t="str">
-        <x:v>8 days</x:v>
+        <x:v>Live</x:v>
       </x:c>
       <x:c r="F27" t="str">
-        <x:v>https://www.coindesk.com/markets/2026/04/24/bitcoin-etfs-just-pulled-usd2-billion-in-8-days-while-short-term-holders-quietly-started-selling</x:v>
+        <x:v>https://finance.yahoo.com/quote/BTC-USD</x:v>
       </x:c>
       <x:c r="G27" t="str">
-        <x:v>CoinDesk.</x:v>
+        <x:v>Updated live snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -7513,19 +7587,19 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>Spot price near</x:v>
+        <x:v>BTC 24H low</x:v>
       </x:c>
       <x:c r="D28" t="str">
-        <x:v>$77.7K</x:v>
+        <x:v>$77,218.00</x:v>
       </x:c>
       <x:c r="E28" t="str">
-        <x:v>Flat/slightly lower</x:v>
+        <x:v>Live</x:v>
       </x:c>
       <x:c r="F28" t="str">
-        <x:v>https://m.economictimes.com/markets/cryptocurrency/bitcoin-holds-near-78000-on-strong-etf-inflows-exchange-reserves-near-record-lows/articleshow/130484642.cms</x:v>
+        <x:v>https://finance.yahoo.com/quote/BTC-USD</x:v>
       </x:c>
       <x:c r="G28" t="str">
-        <x:v>Economic Times.</x:v>
+        <x:v>Updated live snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -7536,19 +7610,19 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>1M performance</x:v>
+        <x:v>ETH/USD</x:v>
       </x:c>
       <x:c r="D29" t="str">
-        <x:v>+10.48%</x:v>
+        <x:v>$2,315.48</x:v>
       </x:c>
       <x:c r="E29" t="str">
-        <x:v>Positive</x:v>
+        <x:v>-0.23%</x:v>
       </x:c>
       <x:c r="F29" t="str">
-        <x:v>https://fortune.com/article/price-of-bitcoin-04-24-2026/</x:v>
+        <x:v>https://finance.yahoo.com/quote/ETH-USD</x:v>
       </x:c>
       <x:c r="G29" t="str">
-        <x:v>Fortune.</x:v>
+        <x:v>Updated live snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -7559,19 +7633,19 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>Open interest</x:v>
+        <x:v>SOL/USD</x:v>
       </x:c>
       <x:c r="D30" t="str">
-        <x:v>N/A</x:v>
+        <x:v>$86.08</x:v>
       </x:c>
       <x:c r="E30" t="str">
-        <x:v>Not sourced</x:v>
+        <x:v>-0.35%</x:v>
       </x:c>
       <x:c r="F30" t="str">
-        <x:v>https://www.investing.com/crypto/bitcoin/historical-data</x:v>
+        <x:v>https://finance.yahoo.com/quote/SOL-USD</x:v>
       </x:c>
       <x:c r="G30" t="str">
-        <x:v>Not included to avoid unsourced value.</x:v>
+        <x:v>Updated live snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -7582,19 +7656,19 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>Key resistance</x:v>
+        <x:v>ETF / liquidity theme</x:v>
       </x:c>
       <x:c r="D31" t="str">
-        <x:v>$80.1K</x:v>
+        <x:v>BTC +13.71% MTD / USDT growth</x:v>
       </x:c>
       <x:c r="E31" t="str">
-        <x:v>STH cost basis</x:v>
+        <x:v>Supportive</x:v>
       </x:c>
       <x:c r="F31" t="str">
-        <x:v>https://www.coindesk.com/markets/2026/04/24/bitcoin-etfs-just-pulled-usd2-billion-in-8-days-while-short-term-holders-quietly-started-selling</x:v>
+        <x:v>https://www.coindesk.com/markets/2026/04/24/bitcoin-is-on-track-for-its-best-month-in-a-year-usd5-billion-usdt-growth-fuels-the-rebound</x:v>
       </x:c>
       <x:c r="G31" t="str">
-        <x:v>CoinDesk.</x:v>
+        <x:v>News backdrop from CoinDesk/Yahoo.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8274,13 +8348,13 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>Investing.com</x:v>
+        <x:v>Yahoo Finance</x:v>
       </x:c>
       <x:c r="D26" t="str">
-        <x:v>Today</x:v>
+        <x:v>9h</x:v>
       </x:c>
       <x:c r="E26" t="str">
-        <x:v>Bitcoin historical data: Apr 24 close 77,518</x:v>
+        <x:v>Bitcoin has one week to secure its best April since 2020</x:v>
       </x:c>
       <x:c r="F26" t="str">
         <x:v>BTC</x:v>
@@ -8289,7 +8363,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="H26" t="str">
-        <x:v>https://www.investing.com/crypto/bitcoin/historical-data</x:v>
+        <x:v>https://finance.yahoo.com/markets/crypto/articles/bitcoin-1-week-secure-best-165709121.html</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -8303,19 +8377,19 @@
         <x:v>CoinDesk</x:v>
       </x:c>
       <x:c r="D27" t="str">
-        <x:v>Today</x:v>
+        <x:v>23h</x:v>
       </x:c>
       <x:c r="E27" t="str">
-        <x:v>Bitcoin ETFs pulled in $2.1B in eight days</x:v>
+        <x:v>Bitcoin is on track for its best month in a year as USDT growth fuels rebound</x:v>
       </x:c>
       <x:c r="F27" t="str">
-        <x:v>ETF</x:v>
+        <x:v>BTC</x:v>
       </x:c>
       <x:c r="G27" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H27" t="str">
-        <x:v>https://www.coindesk.com/markets/2026/04/24/bitcoin-etfs-just-pulled-usd2-billion-in-8-days-while-short-term-holders-quietly-started-selling</x:v>
+        <x:v>https://www.coindesk.com/markets/2026/04/24/bitcoin-is-on-track-for-its-best-month-in-a-year-usd5-billion-usdt-growth-fuels-the-rebound</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -8326,22 +8400,22 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>Economic Times</x:v>
+        <x:v>Benzinga</x:v>
       </x:c>
       <x:c r="D28" t="str">
-        <x:v>Today</x:v>
+        <x:v>Yesterday</x:v>
       </x:c>
       <x:c r="E28" t="str">
-        <x:v>Bitcoin holds near $78,000 on strong ETF inflows</x:v>
+        <x:v>Bitcoin ETFs add $2.1B in eight days as ETF momentum returns</x:v>
       </x:c>
       <x:c r="F28" t="str">
-        <x:v>BTC</x:v>
+        <x:v>ETF</x:v>
       </x:c>
       <x:c r="G28" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="H28" t="str">
-        <x:v>https://m.economictimes.com/markets/cryptocurrency/bitcoin-holds-near-78000-on-strong-etf-inflows-exchange-reserves-near-record-lows/articleshow/130484642.cms</x:v>
+        <x:v>https://www.benzinga.com/crypto/cryptocurrency/26/04/52029356/bitcoin-etfs-add-2-1b-in-8-days-last-time-this-happened-bitcoin-hit-an-all-time-high</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -8352,22 +8426,22 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>Barrons</x:v>
+        <x:v>Yahoo Finance</x:v>
       </x:c>
       <x:c r="D29" t="str">
-        <x:v>Today</x:v>
+        <x:v>Live</x:v>
       </x:c>
       <x:c r="E29" t="str">
-        <x:v>Bitcoin falls as Mideast uncertainty keeps investors cautious</x:v>
+        <x:v>BTC/USD trades near $77.5K with slight 24h weakness</x:v>
       </x:c>
       <x:c r="F29" t="str">
-        <x:v>MACRO</x:v>
+        <x:v>BTC</x:v>
       </x:c>
       <x:c r="G29" t="str">
-        <x:v>Medium</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="H29" t="str">
-        <x:v>https://www.barrons.com/livecoverage/stock-market-news-today-042426/card/bitcoin-falls-as-mideast-uncertainty-keeps-investors-cautious-6AJx1V9dycOi9491vASQ</x:v>
+        <x:v>https://finance.yahoo.com/quote/BTC-USD</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -8378,22 +8452,22 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>Fortune</x:v>
+        <x:v>Yahoo Finance</x:v>
       </x:c>
       <x:c r="D30" t="str">
-        <x:v>Today</x:v>
+        <x:v>Live</x:v>
       </x:c>
       <x:c r="E30" t="str">
-        <x:v>Current price of Bitcoin for April 24, 2026</x:v>
+        <x:v>ETH/USD trades near $2.32K, slightly lower on the day</x:v>
       </x:c>
       <x:c r="F30" t="str">
-        <x:v>BTC</x:v>
+        <x:v>ETH</x:v>
       </x:c>
       <x:c r="G30" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="H30" t="str">
-        <x:v>https://fortune.com/article/price-of-bitcoin-04-24-2026/</x:v>
+        <x:v>https://finance.yahoo.com/quote/ETH-USD</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -8404,22 +8478,22 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>Crypto.news</x:v>
+        <x:v>Yahoo Finance</x:v>
       </x:c>
       <x:c r="D31" t="str">
-        <x:v>Today</x:v>
+        <x:v>Live</x:v>
       </x:c>
       <x:c r="E31" t="str">
-        <x:v>Bitcoin ETFs log 8-day $2.1B inflow streak</x:v>
+        <x:v>SOL/USD trades near $86, slightly lower on the day</x:v>
       </x:c>
       <x:c r="F31" t="str">
-        <x:v>ETF</x:v>
+        <x:v>SOL</x:v>
       </x:c>
       <x:c r="G31" t="str">
         <x:v>Medium</x:v>
       </x:c>
       <x:c r="H31" t="str">
-        <x:v>https://crypto.news/bitcoin-etfs-log-8-day-2-1b-inflow-streak/</x:v>
+        <x:v>https://finance.yahoo.com/quote/SOL-USD</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8667,13 +8741,13 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>BTC was slightly lower on the day</x:v>
+        <x:v>BTC live tape is slightly softer</x:v>
       </x:c>
       <x:c r="D14" t="str">
-        <x:v>Investing.com BTC/USD historical data showed Apr 24 close at 77,518.0, down 0.95%.</x:v>
+        <x:v>BTC trades at $77,519.00, down -0.11% versus previous close; 24h range is $77,218.00-$77,878.00.</x:v>
       </x:c>
       <x:c r="E14" t="str">
-        <x:v>https://www.investing.com/crypto/bitcoin/historical-data</x:v>
+        <x:v>https://finance.yahoo.com/quote/BTC-USD</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -8684,13 +8758,13 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>ETF demand supported the broader trend</x:v>
+        <x:v>ETF and liquidity backdrop remains supportive</x:v>
       </x:c>
       <x:c r="D15" t="str">
-        <x:v>CoinDesk reported U.S. spot Bitcoin ETFs pulled in roughly $2.1B over eight straight inflow days through Apr 23.</x:v>
+        <x:v>CoinDesk/Yahoo reported Bitcoin is on track for one of its strongest Aprils, with ETF/stablecoin liquidity themes supporting the rebound.</x:v>
       </x:c>
       <x:c r="E15" t="str">
-        <x:v>https://www.coindesk.com/markets/2026/04/24/bitcoin-etfs-just-pulled-usd2-billion-in-8-days-while-short-term-holders-quietly-started-selling</x:v>
+        <x:v>https://www.coindesk.com/markets/2026/04/24/bitcoin-is-on-track-for-its-best-month-in-a-year-usd5-billion-usdt-growth-fuels-the-rebound</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -8701,13 +8775,13 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>Geopolitics limited risk appetite</x:v>
+        <x:v>Altcoins are also soft intraday</x:v>
       </x:c>
       <x:c r="D16" t="str">
-        <x:v>Barrons reported Bitcoin was slightly lower as Middle East uncertainty kept risk appetite cautious.</x:v>
+        <x:v>ETH is -0.23% and SOL is -0.35% in the latest snapshot, so the current tape is not purely BTC-specific.</x:v>
       </x:c>
       <x:c r="E16" t="str">
-        <x:v>https://www.barrons.com/livecoverage/stock-market-news-today-042426/card/bitcoin-falls-as-mideast-uncertainty-keeps-investors-cautious-6AJx1V9dycOi9491vASQ</x:v>
+        <x:v>https://finance.yahoo.com/quote/ETH-USD</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8848,22 +8922,22 @@
         <x:v>Crypto</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>Bullish medium term, soft daily tape</x:v>
+        <x:v>Constructive medium term, soft live tape</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>BTC was slightly down on Apr 24, but ETF inflows remain a major support.</x:v>
+        <x:v>BTC is slightly lower in the latest live snapshot at $77,519.00, but remains near the $77K-$78K zone.</x:v>
       </x:c>
       <x:c r="D6" t="str">
-        <x:v>Near-term resistance sits around the 80k area, where short-term holder supply matters.</x:v>
+        <x:v>ETF inflow and stablecoin liquidity themes still support the broader April rebound narrative.</x:v>
       </x:c>
       <x:c r="E6" t="str">
-        <x:v>Best tactical stance: constructive but avoid chasing into resistance without flow confirmation.</x:v>
+        <x:v>Near-term risk: weekend liquidity and geopolitical headlines can exaggerate moves.</x:v>
       </x:c>
       <x:c r="F6" t="str">
-        <x:v>Base case: BTC remains supported by ETF demand but vulnerable to risk-off headlines.</x:v>
+        <x:v>Base case: do not chase; keep constructive bias while BTC holds the mid-70K area and ETF flows remain supportive.</x:v>
       </x:c>
       <x:c r="G6" t="str">
-        <x:v>https://www.coindesk.com/markets/2026/04/24/bitcoin-etfs-just-pulled-usd2-billion-in-8-days-while-short-term-holders-quietly-started-selling</x:v>
+        <x:v>https://www.coindesk.com/markets/2026/04/24/bitcoin-is-on-track-for-its-best-month-in-a-year-usd5-billion-usdt-growth-fuels-the-rebound</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
